--- a/光伏配储项目/电价数据/2026/蕉岭站.xlsx
+++ b/光伏配储项目/电价数据/2026/蕉岭站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.43236</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78608</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.47956</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.50052</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4442</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.38093</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36766</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35873</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36846</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37825</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34072</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38699</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.3904</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.40103</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.42204</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36424</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31089</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24221</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.13746</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.00199</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.07884000000000001</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.08263</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.06822</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.51263</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55748</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7414500000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14388</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39618</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.36418</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43368</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44044</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66704</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8899</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21494</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.34744</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17734</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.0326</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.30916</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41036</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.70573</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.12258</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.9507599999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.9096599999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.80691</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76913</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5189400000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48975</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46976</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43102</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.73109</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90715</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.97084</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51249</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.54053</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.51975</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5199</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50124</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48183</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38394</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39178</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.50704</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38654</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38635</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.47395</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.43095</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.42978</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42648</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.50441</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.56908</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.46468</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.4492</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.54539</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5614199999999999</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38536</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36858</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40155</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49615</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33683</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.03908</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.04728</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30835</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.18191</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.07223</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.43919</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.57973</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.19103</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.02883</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.00069</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6029099999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.7679199999999999</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.79723</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18804</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.39694</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14098</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.8612000000000001</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.2283</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12533</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.20975</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.9659099999999999</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.10959</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66859</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00295</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.92747</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9799600000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.81509</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.29287</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.27687</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4548</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.25191</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45444</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43259</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44847</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37952</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33543</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.52162</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5006</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.49975</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37239</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45169</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42056</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39529</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3889</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43799</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45507</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.40361</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37299</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35565</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40123</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.40044</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48625</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45072</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44785</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34884</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35553</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22381</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36816</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7981200000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.03688</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.3871</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3711</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32316</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62871</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.66695</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46972</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50731</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>-0.00758</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43666</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50583</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.62926</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.49395</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.26689</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.23431</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.18728</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.05047</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43689</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46181</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39991</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34296</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5234500000000001</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5106000000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44499</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39714</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40038</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45901</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36649</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36347</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34112</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39251</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35393</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39837</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42209</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43658</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35838</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41631</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.04408</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.59375</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40363</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.2147</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.18723</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.28856</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36626</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6419199999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31374</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.09949</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.07321</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.41174</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.10048</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44435</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.23122</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47532</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52686</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47451</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40425</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.11834</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.23329</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.41176</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.5340199999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.52278</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.4947</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5046</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44714</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42467</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41658</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33095</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37984</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31668</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28543</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30472</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27051</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.26049</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.06775</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13253</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03758</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.05454</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.05632</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.29792</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.34056</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.36917</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.33202</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.29123</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37577</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.06853000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.22342</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.08273</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.11157</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.08373999999999999</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.23304</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.08270000000000001</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.02289</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.16642</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.29414</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.06277000000000001</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.18521</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.12215</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.09283</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.25554</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.05997</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.18009</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.20937</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.09243000000000001</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.22946</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1015</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04279</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29371</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.005860000000000001</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19828</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04532</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26372</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14075</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01063</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05242</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.0506</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34579</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.30063</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.28037</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33507</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43068</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46059</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78574</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86973</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6136699999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5561699999999999</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42034</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3443</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.36653</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.37091</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.31002</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.2475</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.43824</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.26135</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.23497</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8914800000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47655</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.19037</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.4102</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.12947</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.83509</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.31484</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.22551</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.09295</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.28124</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.17124</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60137</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.31678</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.30574</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.27361</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30043</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.26202</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.28524</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.07468999999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.2256</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.22114</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.24174</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.21378</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.24741</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.21923</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.21768</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.19813</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.21627</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.23877</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.22469</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.30043</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.86229</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.28641</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.24269</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.2765</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.22055</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.2594</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.23897</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.28572</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.27669</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.2745</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.28158</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.25237</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.27825</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.26722</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.21285</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.17984</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.26396</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.2269</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2617</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.25653</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.24067</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.25621</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.2677</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.28637</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.28023</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.27463</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.29457</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.29626</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.09919</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26004</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.25337</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27189</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.14053</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25977</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20411</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33189</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2918</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.27378</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.09865</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30331</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.28872</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.28176</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.26865</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.28967</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28544</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.2575</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.2725</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.26599</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.27439</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.20316</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.31503</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.27181</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.24647</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.23613</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.07893</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.13715</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.80889</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.45235</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.17242</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6792100000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7730399999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.62905</v>
+      </c>
+      <c r="I126" t="n">
+        <v>-0.03416</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.05525</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.41747</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.46969</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.29084</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.19139</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.39473</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.21483</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.18568</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.17254</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.37829</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.18627</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.37039</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.20905</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.18481</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.20133</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4525</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.03545</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.21554</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.27246</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.28398</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.27477</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25542</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.13753</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.25493</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27744</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.04469</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26922</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26552</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28777</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.28301</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29668</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.28009</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.23104</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.31595</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.22711</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.31728</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.23761</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.22085</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.20128</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.26218</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.26268</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.21942</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.26138</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.20689</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.15666</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.19355</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.18106</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.02599</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.28173</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.08126</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.07825</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.06947</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.07679999999999999</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.0211</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.17544</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.19941</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.19644</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.27214</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.26813</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.02686</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.02618</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.26766</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.08685</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.03025</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.09440999999999999</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.04008</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.03146</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.20679</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.29137</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.15906</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.22715</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.0225</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.26747</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.27296</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.03024</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.13243</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>-0.01584</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>-0.01202</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.04156</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28677</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.03363</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.02122</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>-0.00235</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27187</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.01816</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20055</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.01799</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25789</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.03909000000000001</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04312</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>-0.0281</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04451</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.01138</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.25391</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.22251</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.25308</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.23734</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.25542</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.22522</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.2013</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.26497</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.24446</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.26839</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.23462</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.2267</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.17706</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.22823</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.19172</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.18355</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.19151</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.19117</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39021</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.23052</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.17368</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.22947</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.25135</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.13707</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.1881</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.2196</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.24368</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.23912</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.24188</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.23861</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.32616</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.25354</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.26256</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.24288</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.25303</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.23447</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.25411</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.25582</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.25655</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.2572</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.25884</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.25761</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.25884</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.26206</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.1865</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.23817</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.23948</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.25364</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.27101</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.25285</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.2712</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.26899</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.27137</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.27023</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.26518</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31539</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.29601</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23598</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25872</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18387</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14332</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.26261</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.17951</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.06071</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21692</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28183</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.24845</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.24125</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.16258</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.26902</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.28503</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.28557</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.31313</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.31697</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.30613</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.28611</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.30018</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.15385</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.32298</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41326</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.17963</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.27241</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.2703</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.2827</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.29868</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.29516</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.29215</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.21629</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.25436</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.25287</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.26953</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.26244</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.30362</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.26305</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.13789</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.16003</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.25775</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.26622</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.22366</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.24078</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.23604</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.25169</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.2601</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.26045</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.25126</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.2583</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.25837</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.25898</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.25373</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.21849</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.25142</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.26566</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.26806</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.38827</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08657</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.63244</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.46424</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.39326</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.47201</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.27044</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.17909</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.30449</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.02802</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.55926</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.34118</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.44987</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.26264</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.27496</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.30707</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.5584199999999999</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.4531</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.44391</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.42513</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.69396</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.3629</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.3927</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47451</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.21924</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.32202</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32158</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.27788</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.29117</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04331</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.225</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.23174</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.17631</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.23301</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.23468</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.22599</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2081</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.08444</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.07895999999999999</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.22623</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.22525</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.23052</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.23026</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.23128</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.23294</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.08016</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.27166</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.08053</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.01968</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.16882</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.27003</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.2123</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.08026000000000001</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.08685</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.12179</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.08697000000000001</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.02384</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.02072</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.10973</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.16379</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.2502</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.32837</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.23606</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.30051</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.19395</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.15133</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.30419</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.30475</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2922</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.25871</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.22244</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.2794</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.2867</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.29037</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.10472</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.25174</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.26431</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.17169</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.23663</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.24812</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.2569</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.27553</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.2556</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.05425</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.11719</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.28508</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.19794</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.29852</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.17879</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.29971</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.19736</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.17246</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.18606</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.06214</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.29447</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.16932</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.0579</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>-0.02444</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.2882</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.11167</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.2878</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.24219</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.2885</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.28943</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.28812</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.20735</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.28747</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.28432</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.2258</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.21713</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.20598</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.27765</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.27812</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.22789</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.19116</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.26246</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.22387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.27767</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.21327</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.23044</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.2019</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.22891</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.22592</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.2249</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.2744</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.2166</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.21621</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.21512</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.242</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.21232</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.22915</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.22957</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.26867</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.28245</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.28249</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.29507</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.28233</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.24367</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30153</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.30214</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.30099</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.30197</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.29301</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.26214</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.30119</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.27789</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.28803</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.27131</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.26921</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.2301</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.25467</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.22464</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.25887</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5930700000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.00297</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.2188</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.03894</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.1925</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.29402</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.24562</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.34936</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.30027</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.29708</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.26724</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.29821</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.2612</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.29803</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.19173</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.23394</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.30411</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.31811</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.28941</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.29613</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.22589</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25066</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03582</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.2830299999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.07945000000000001</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.00243</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20499</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.05049</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15276</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21448</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.2012</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2718</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.28989</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.28839</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26238</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.23603</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.26405</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.27643</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.24439</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.31782</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.24967</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.18219</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.19235</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.28361</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.43024</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.62002</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.57775</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6093099999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.14634</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.7838200000000001</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.1838</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>-0.03928</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.10477</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46436</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.37637</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.21261</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.17005</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.22929</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.23735</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.27513</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.32196</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.27758</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.27879</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.2059</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.16162</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.18595</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.08771999999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.24524</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.24231</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.24311</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.26041</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.27421</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.27576</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.22626</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.24837</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.22673</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.24646</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.22828</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.23172</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.21334</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.15115</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.17898</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.08981</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.20359</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.16581</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.20626</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.40329</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.38464</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42116</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43909</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.50241</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.26729</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.01612</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.22944</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.27436</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40661</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65777</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.37886</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.72017</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.05251</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.28423</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.21651</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33991</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.02514</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.23782</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.29561</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.29389</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.06714000000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.07041</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.05276</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.04509000000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.0849</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.23842</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.20046</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.20634</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.17475</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.16913</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.14407</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.02577</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.03793</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>-0.01036</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.04854</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.09556999999999999</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>-0.03272</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.71494</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.56902</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6193099999999999</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.16414</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.16864</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.18908</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.20066</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.19638</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.15409</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.23841</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.22725</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.2113</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.21464</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.36304</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.11932</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.20081</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.20269</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.24738</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.26406</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.20144</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.22448</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.18985</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.19956</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.23324</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.30209</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.01286</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.26602</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.30151</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.00752</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.02871</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.22717</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02623</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37463</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36402</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.35368</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.21457</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.10404</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.04009</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.04132</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.04045</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.17345</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.27565</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.26714</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.25889</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.26253</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.22569</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.11243</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.12569</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.2846</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.10732</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.09676999999999999</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.12228</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.18027</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.20537</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.12833</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.18543</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.23234</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.20504</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.03453</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.24179</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.03501</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.04326</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.04043</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.10388</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.08127</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.15745</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.11447</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.16484</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.10552</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.12789</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.09631000000000001</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.02376</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.18754</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.02429</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.08609</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.02279</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.02019</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.08343</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.02093</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.02277</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.02369</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.02741</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.07579999999999999</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.0174</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.01496</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.00376</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.008970000000000001</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>-0.02036</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.00649</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.03542</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04574</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.00124</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.213</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>-0.03282</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28632</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25531</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.04701</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.02454</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.26601</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>-0.00962</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.1632</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.01338</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.01202</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>-0.01093</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>-0.00296</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.01423</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.04137</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.26693</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.25327</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.26778</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.15883</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.19569</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.21453</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.22647</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.26211</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.16895</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.21972</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.18856</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.19318</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.09812</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.12474</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.10131</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.14038</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.17714</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.22021</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.1854</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.16729</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.02791</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.03164</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.18386</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.02416</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.22353</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.02567</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.14598</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.15632</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.20272</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.23387</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.22947</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.22068</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.07578</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.07429999999999999</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.22781</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.12009</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.15389</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.14133</v>
+      </c>
+      <c r="P136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.11385</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.07313</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.28307</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.22278</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.02651</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00088</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.15599</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02272</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01431</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03821</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00263</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03562</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01159</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03528</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20791</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.2941</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.26999</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26485</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.27554</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.27548</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.26706</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25419</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.24609</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.27161</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.25921</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.27255</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.21749</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29013</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.26463</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28208</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.27302</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26606</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.25041</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.28359</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.209</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.04322</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.02705</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.21484</v>
+      </c>
+      <c r="F137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.16748</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.19725</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.15062</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.20048</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.0207</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.29765</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.02454</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.02638</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.02559</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.02003</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.03411</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21388</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.10866</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.83875</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.87171</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.33746</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03826</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.16583</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04851</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00244</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04733</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31308</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.3066</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.27498</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.28633</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.28733</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.2766</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>-0.04053</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.30402</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.01136</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.12079</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.9268200000000001</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.04283</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.12385</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.78918</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.78743</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.79155</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.88797</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.01994</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.11978</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.03964</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.28439</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.25438</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.25422</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.20723</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.08211</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.07578</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44652</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.15851</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.18376</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.15403</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.16037</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.03227</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.18831</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.17399</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.17124</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.11519</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.05155</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.08767</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.02416</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.08494</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.02224</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.02326</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>-0.02016</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.0294</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.10332</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.16886</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.09863</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.1204</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.12193</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.1846</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.2245</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.13364</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.0709</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.28754</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.11993</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.10538</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.2516</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28417</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30033</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.2902</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25983</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30351</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.30522</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31925</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.31116</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.30427</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.30168</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32378</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36959</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.1765</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.22602</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.06548000000000001</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.20156</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.24759</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.21258</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.20982</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.15297</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.24829</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.24335</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.23009</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.23579</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.2804700000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.25958</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.27213</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.27094</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.28221</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.26967</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.26588</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.26587</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.27487</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.29819</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.26072</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.26105</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.2513</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.26043</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.26051</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.26201</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.26252</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.26541</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.27588</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.18275</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.25967</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.07945000000000001</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.38726</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.06053</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.14206</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.17199</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.26411</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.28761</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.31113</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.29702</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30607</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.32307</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.38855</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.40988</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.7706000000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.55091</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.23756</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.4972200000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.83026</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.25833</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.34589</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.15637</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.21549</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.20448</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.22176</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.15234</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.32524</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.26919</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.27423</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.15987</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.27542</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.26388</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.27352</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.26282</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.26342</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.27892</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.26365</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.27333</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.27198</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.28159</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.27894</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.2785</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.26373</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.26137</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.25587</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.24909</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.29732</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.23757</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.2319</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.24356</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.30851</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.30608</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39064</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35338</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43416</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.33213</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.31096</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33412</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33779</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.34258</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.37499</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45337</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.74451</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.5596100000000001</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.33853</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.40414</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.36376</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.40681</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.81311</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.73072</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.58239</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.40448</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.22253</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.29476</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.28133</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.27972</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.26401</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3181</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.26469</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.29815</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.23327</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.2453</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.23933</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.25982</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.25157</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.2331</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3013</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.25589</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.26092</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.24439</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.24339</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.23145</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29203</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.30576</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.22735</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.21537</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26286</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.26223</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.32029</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24339</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.20888</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19687</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24922</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.0321</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.17327</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27714</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03111</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01884</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.17679</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.19434</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03527</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0568</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.27568</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23498</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25187</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34902</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42439</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.4065299999999999</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.47561</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.41428</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.38698</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40729</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.43113</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.44088</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37457</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43702</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3743</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.36463</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34568</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.33408</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.75848</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.37556</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.40919</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.38141</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34714</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34933</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.3318</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34318</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.2674</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.15315</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30218</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23784</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.1164</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27806</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.42002</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43692</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4323</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43667</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34217</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37244</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.38488</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36535</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.37332</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.36083</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33966</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.34174</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37294</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34763</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34708</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33938</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33948</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33726</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30773</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30862</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17678</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30262</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28911</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14641</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19961</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2372</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04743</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04763000000000001</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17749</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04888</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15791</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24189</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04994</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20208</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04672999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27628</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32405</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47595</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.39379</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39395</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40466</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38063</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.41432</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.40333</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.43951</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41598</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42157</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40895</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.46782</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.36602</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.37214</v>
       </c>
     </row>
   </sheetData>
